--- a/5. Other/ICCID_ESIM/ICCID_ESIM_TG102LE-4G_SL300_LO4.xlsx
+++ b/5. Other/ICCID_ESIM/ICCID_ESIM_TG102LE-4G_SL300_LO4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\ICCID_ESIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61646640-CFD5-4B1D-84A6-8910B13BB1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32906651-4940-4067-AB9C-4E3B75D43B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1204">
   <si>
     <t>IMEI_LE4G</t>
   </si>
@@ -2768,6 +2768,909 @@
   </si>
   <si>
     <t>8984020001150021501</t>
+  </si>
+  <si>
+    <t>SĐT</t>
+  </si>
+  <si>
+    <t>01388707656</t>
+  </si>
+  <si>
+    <t>01388707657</t>
+  </si>
+  <si>
+    <t>01388707658</t>
+  </si>
+  <si>
+    <t>01388707659</t>
+  </si>
+  <si>
+    <t>01388707660</t>
+  </si>
+  <si>
+    <t>01388707661</t>
+  </si>
+  <si>
+    <t>01388707662</t>
+  </si>
+  <si>
+    <t>01388707663</t>
+  </si>
+  <si>
+    <t>01388707664</t>
+  </si>
+  <si>
+    <t>01388707665</t>
+  </si>
+  <si>
+    <t>01388707666</t>
+  </si>
+  <si>
+    <t>01388707667</t>
+  </si>
+  <si>
+    <t>01388707668</t>
+  </si>
+  <si>
+    <t>01388707669</t>
+  </si>
+  <si>
+    <t>01388707670</t>
+  </si>
+  <si>
+    <t>01388707671</t>
+  </si>
+  <si>
+    <t>01388707672</t>
+  </si>
+  <si>
+    <t>01388707673</t>
+  </si>
+  <si>
+    <t>01388707674</t>
+  </si>
+  <si>
+    <t>01388707675</t>
+  </si>
+  <si>
+    <t>01388707676</t>
+  </si>
+  <si>
+    <t>01388707677</t>
+  </si>
+  <si>
+    <t>01388707678</t>
+  </si>
+  <si>
+    <t>01388707679</t>
+  </si>
+  <si>
+    <t>01388707680</t>
+  </si>
+  <si>
+    <t>01388707681</t>
+  </si>
+  <si>
+    <t>01388707682</t>
+  </si>
+  <si>
+    <t>01388707683</t>
+  </si>
+  <si>
+    <t>01388707684</t>
+  </si>
+  <si>
+    <t>01388707685</t>
+  </si>
+  <si>
+    <t>01388707686</t>
+  </si>
+  <si>
+    <t>01388707687</t>
+  </si>
+  <si>
+    <t>01388707688</t>
+  </si>
+  <si>
+    <t>01388707689</t>
+  </si>
+  <si>
+    <t>01388707690</t>
+  </si>
+  <si>
+    <t>01388707691</t>
+  </si>
+  <si>
+    <t>01388707692</t>
+  </si>
+  <si>
+    <t>01388707693</t>
+  </si>
+  <si>
+    <t>01388707694</t>
+  </si>
+  <si>
+    <t>01388707695</t>
+  </si>
+  <si>
+    <t>01388707696</t>
+  </si>
+  <si>
+    <t>01388707697</t>
+  </si>
+  <si>
+    <t>01388707698</t>
+  </si>
+  <si>
+    <t>01388707699</t>
+  </si>
+  <si>
+    <t>01388707700</t>
+  </si>
+  <si>
+    <t>01388707701</t>
+  </si>
+  <si>
+    <t>01388707702</t>
+  </si>
+  <si>
+    <t>01388707703</t>
+  </si>
+  <si>
+    <t>01388707704</t>
+  </si>
+  <si>
+    <t>01388707705</t>
+  </si>
+  <si>
+    <t>01388707706</t>
+  </si>
+  <si>
+    <t>01388707707</t>
+  </si>
+  <si>
+    <t>01388707708</t>
+  </si>
+  <si>
+    <t>01388707709</t>
+  </si>
+  <si>
+    <t>01388707710</t>
+  </si>
+  <si>
+    <t>01388707711</t>
+  </si>
+  <si>
+    <t>01388707712</t>
+  </si>
+  <si>
+    <t>01388707713</t>
+  </si>
+  <si>
+    <t>01388707714</t>
+  </si>
+  <si>
+    <t>01388707715</t>
+  </si>
+  <si>
+    <t>01388707716</t>
+  </si>
+  <si>
+    <t>01388707717</t>
+  </si>
+  <si>
+    <t>01388707718</t>
+  </si>
+  <si>
+    <t>01388707719</t>
+  </si>
+  <si>
+    <t>01388707720</t>
+  </si>
+  <si>
+    <t>01388707721</t>
+  </si>
+  <si>
+    <t>01388707722</t>
+  </si>
+  <si>
+    <t>01388707723</t>
+  </si>
+  <si>
+    <t>01388707724</t>
+  </si>
+  <si>
+    <t>01388707725</t>
+  </si>
+  <si>
+    <t>01388707726</t>
+  </si>
+  <si>
+    <t>01388707727</t>
+  </si>
+  <si>
+    <t>01388707728</t>
+  </si>
+  <si>
+    <t>01388707729</t>
+  </si>
+  <si>
+    <t>01388707730</t>
+  </si>
+  <si>
+    <t>01388707731</t>
+  </si>
+  <si>
+    <t>01388707732</t>
+  </si>
+  <si>
+    <t>01388707733</t>
+  </si>
+  <si>
+    <t>01388707734</t>
+  </si>
+  <si>
+    <t>01388707735</t>
+  </si>
+  <si>
+    <t>01388707736</t>
+  </si>
+  <si>
+    <t>01388707737</t>
+  </si>
+  <si>
+    <t>01388707738</t>
+  </si>
+  <si>
+    <t>01388707739</t>
+  </si>
+  <si>
+    <t>01388707740</t>
+  </si>
+  <si>
+    <t>01388707741</t>
+  </si>
+  <si>
+    <t>01388707742</t>
+  </si>
+  <si>
+    <t>01388707743</t>
+  </si>
+  <si>
+    <t>01388707744</t>
+  </si>
+  <si>
+    <t>01388707745</t>
+  </si>
+  <si>
+    <t>01388707746</t>
+  </si>
+  <si>
+    <t>01388707747</t>
+  </si>
+  <si>
+    <t>01388707748</t>
+  </si>
+  <si>
+    <t>01388707749</t>
+  </si>
+  <si>
+    <t>01388707750</t>
+  </si>
+  <si>
+    <t>01388707751</t>
+  </si>
+  <si>
+    <t>01388707752</t>
+  </si>
+  <si>
+    <t>01388707753</t>
+  </si>
+  <si>
+    <t>01388707754</t>
+  </si>
+  <si>
+    <t>01388707755</t>
+  </si>
+  <si>
+    <t>01388702100</t>
+  </si>
+  <si>
+    <t>01388702101</t>
+  </si>
+  <si>
+    <t>01388702102</t>
+  </si>
+  <si>
+    <t>01388702103</t>
+  </si>
+  <si>
+    <t>01388702104</t>
+  </si>
+  <si>
+    <t>01388702105</t>
+  </si>
+  <si>
+    <t>01388702106</t>
+  </si>
+  <si>
+    <t>01388702107</t>
+  </si>
+  <si>
+    <t>01388702108</t>
+  </si>
+  <si>
+    <t>01388702109</t>
+  </si>
+  <si>
+    <t>01388702110</t>
+  </si>
+  <si>
+    <t>01388702111</t>
+  </si>
+  <si>
+    <t>01388702112</t>
+  </si>
+  <si>
+    <t>01388702113</t>
+  </si>
+  <si>
+    <t>01388702114</t>
+  </si>
+  <si>
+    <t>01388702115</t>
+  </si>
+  <si>
+    <t>01388702116</t>
+  </si>
+  <si>
+    <t>01388702117</t>
+  </si>
+  <si>
+    <t>01388702118</t>
+  </si>
+  <si>
+    <t>01388702119</t>
+  </si>
+  <si>
+    <t>01388702120</t>
+  </si>
+  <si>
+    <t>01388702121</t>
+  </si>
+  <si>
+    <t>01388702122</t>
+  </si>
+  <si>
+    <t>01388702123</t>
+  </si>
+  <si>
+    <t>01388702124</t>
+  </si>
+  <si>
+    <t>01388702125</t>
+  </si>
+  <si>
+    <t>01388702126</t>
+  </si>
+  <si>
+    <t>01388702127</t>
+  </si>
+  <si>
+    <t>01388702128</t>
+  </si>
+  <si>
+    <t>01388702129</t>
+  </si>
+  <si>
+    <t>01388702130</t>
+  </si>
+  <si>
+    <t>01388702131</t>
+  </si>
+  <si>
+    <t>01388702132</t>
+  </si>
+  <si>
+    <t>01388702133</t>
+  </si>
+  <si>
+    <t>01388702134</t>
+  </si>
+  <si>
+    <t>01388702135</t>
+  </si>
+  <si>
+    <t>01388702136</t>
+  </si>
+  <si>
+    <t>01388702137</t>
+  </si>
+  <si>
+    <t>01388702138</t>
+  </si>
+  <si>
+    <t>01388702139</t>
+  </si>
+  <si>
+    <t>01388702140</t>
+  </si>
+  <si>
+    <t>01388702141</t>
+  </si>
+  <si>
+    <t>01388702142</t>
+  </si>
+  <si>
+    <t>01388702143</t>
+  </si>
+  <si>
+    <t>01388702144</t>
+  </si>
+  <si>
+    <t>01388702145</t>
+  </si>
+  <si>
+    <t>01388702146</t>
+  </si>
+  <si>
+    <t>01388702147</t>
+  </si>
+  <si>
+    <t>01388702148</t>
+  </si>
+  <si>
+    <t>01388702149</t>
+  </si>
+  <si>
+    <t>01388702150</t>
+  </si>
+  <si>
+    <t>01388702151</t>
+  </si>
+  <si>
+    <t>01388702152</t>
+  </si>
+  <si>
+    <t>01388702153</t>
+  </si>
+  <si>
+    <t>01388702154</t>
+  </si>
+  <si>
+    <t>01388702155</t>
+  </si>
+  <si>
+    <t>01388702156</t>
+  </si>
+  <si>
+    <t>01388702157</t>
+  </si>
+  <si>
+    <t>01388702158</t>
+  </si>
+  <si>
+    <t>01388702159</t>
+  </si>
+  <si>
+    <t>01388702160</t>
+  </si>
+  <si>
+    <t>01388702161</t>
+  </si>
+  <si>
+    <t>01388702162</t>
+  </si>
+  <si>
+    <t>01388702163</t>
+  </si>
+  <si>
+    <t>01388702164</t>
+  </si>
+  <si>
+    <t>01388702165</t>
+  </si>
+  <si>
+    <t>01388702166</t>
+  </si>
+  <si>
+    <t>01388702167</t>
+  </si>
+  <si>
+    <t>01388702168</t>
+  </si>
+  <si>
+    <t>01388702169</t>
+  </si>
+  <si>
+    <t>01388702170</t>
+  </si>
+  <si>
+    <t>01388702171</t>
+  </si>
+  <si>
+    <t>01388702172</t>
+  </si>
+  <si>
+    <t>01388702173</t>
+  </si>
+  <si>
+    <t>01388702174</t>
+  </si>
+  <si>
+    <t>01388702175</t>
+  </si>
+  <si>
+    <t>01388702176</t>
+  </si>
+  <si>
+    <t>01388702177</t>
+  </si>
+  <si>
+    <t>01388702178</t>
+  </si>
+  <si>
+    <t>01388702179</t>
+  </si>
+  <si>
+    <t>01388702180</t>
+  </si>
+  <si>
+    <t>01388702181</t>
+  </si>
+  <si>
+    <t>01388702182</t>
+  </si>
+  <si>
+    <t>01388702183</t>
+  </si>
+  <si>
+    <t>01388702184</t>
+  </si>
+  <si>
+    <t>01388702185</t>
+  </si>
+  <si>
+    <t>01388702186</t>
+  </si>
+  <si>
+    <t>01388702187</t>
+  </si>
+  <si>
+    <t>01388702188</t>
+  </si>
+  <si>
+    <t>01388702189</t>
+  </si>
+  <si>
+    <t>01388702190</t>
+  </si>
+  <si>
+    <t>01388702191</t>
+  </si>
+  <si>
+    <t>01388702192</t>
+  </si>
+  <si>
+    <t>01388702193</t>
+  </si>
+  <si>
+    <t>01388702194</t>
+  </si>
+  <si>
+    <t>01388702195</t>
+  </si>
+  <si>
+    <t>01388702196</t>
+  </si>
+  <si>
+    <t>01388702197</t>
+  </si>
+  <si>
+    <t>01388702198</t>
+  </si>
+  <si>
+    <t>01388702199</t>
+  </si>
+  <si>
+    <t>01388725434</t>
+  </si>
+  <si>
+    <t>01388725435</t>
+  </si>
+  <si>
+    <t>01388725436</t>
+  </si>
+  <si>
+    <t>01388725437</t>
+  </si>
+  <si>
+    <t>01388725438</t>
+  </si>
+  <si>
+    <t>01388725439</t>
+  </si>
+  <si>
+    <t>01388725440</t>
+  </si>
+  <si>
+    <t>01388725441</t>
+  </si>
+  <si>
+    <t>01388725442</t>
+  </si>
+  <si>
+    <t>01388725443</t>
+  </si>
+  <si>
+    <t>01388725444</t>
+  </si>
+  <si>
+    <t>01388725445</t>
+  </si>
+  <si>
+    <t>01388725446</t>
+  </si>
+  <si>
+    <t>01388725447</t>
+  </si>
+  <si>
+    <t>01388725448</t>
+  </si>
+  <si>
+    <t>01388725449</t>
+  </si>
+  <si>
+    <t>01388725450</t>
+  </si>
+  <si>
+    <t>01388725451</t>
+  </si>
+  <si>
+    <t>01388725452</t>
+  </si>
+  <si>
+    <t>01388725453</t>
+  </si>
+  <si>
+    <t>01388725454</t>
+  </si>
+  <si>
+    <t>01388725455</t>
+  </si>
+  <si>
+    <t>01388725456</t>
+  </si>
+  <si>
+    <t>01388725457</t>
+  </si>
+  <si>
+    <t>01388725458</t>
+  </si>
+  <si>
+    <t>01388725459</t>
+  </si>
+  <si>
+    <t>01388725460</t>
+  </si>
+  <si>
+    <t>01388725461</t>
+  </si>
+  <si>
+    <t>01388725462</t>
+  </si>
+  <si>
+    <t>01388725463</t>
+  </si>
+  <si>
+    <t>01388725464</t>
+  </si>
+  <si>
+    <t>01388725465</t>
+  </si>
+  <si>
+    <t>01388725466</t>
+  </si>
+  <si>
+    <t>01388725467</t>
+  </si>
+  <si>
+    <t>01388725468</t>
+  </si>
+  <si>
+    <t>01388725469</t>
+  </si>
+  <si>
+    <t>01388725470</t>
+  </si>
+  <si>
+    <t>01388725471</t>
+  </si>
+  <si>
+    <t>01388725472</t>
+  </si>
+  <si>
+    <t>01388725473</t>
+  </si>
+  <si>
+    <t>01388725474</t>
+  </si>
+  <si>
+    <t>01388725475</t>
+  </si>
+  <si>
+    <t>01388725476</t>
+  </si>
+  <si>
+    <t>01388725477</t>
+  </si>
+  <si>
+    <t>01388725478</t>
+  </si>
+  <si>
+    <t>01388725479</t>
+  </si>
+  <si>
+    <t>01388725480</t>
+  </si>
+  <si>
+    <t>01388725481</t>
+  </si>
+  <si>
+    <t>01388725482</t>
+  </si>
+  <si>
+    <t>01388725483</t>
+  </si>
+  <si>
+    <t>01388725484</t>
+  </si>
+  <si>
+    <t>01388725485</t>
+  </si>
+  <si>
+    <t>01388725486</t>
+  </si>
+  <si>
+    <t>01388725487</t>
+  </si>
+  <si>
+    <t>01388725488</t>
+  </si>
+  <si>
+    <t>01388725489</t>
+  </si>
+  <si>
+    <t>01388725490</t>
+  </si>
+  <si>
+    <t>01388725491</t>
+  </si>
+  <si>
+    <t>01388725492</t>
+  </si>
+  <si>
+    <t>01388725493</t>
+  </si>
+  <si>
+    <t>01388725494</t>
+  </si>
+  <si>
+    <t>01388725495</t>
+  </si>
+  <si>
+    <t>01388725496</t>
+  </si>
+  <si>
+    <t>01388725497</t>
+  </si>
+  <si>
+    <t>01388725498</t>
+  </si>
+  <si>
+    <t>01388725499</t>
+  </si>
+  <si>
+    <t>01388725500</t>
+  </si>
+  <si>
+    <t>01388725501</t>
+  </si>
+  <si>
+    <t>01388725502</t>
+  </si>
+  <si>
+    <t>01388725503</t>
+  </si>
+  <si>
+    <t>01388725504</t>
+  </si>
+  <si>
+    <t>01388725505</t>
+  </si>
+  <si>
+    <t>01388725506</t>
+  </si>
+  <si>
+    <t>01388725507</t>
+  </si>
+  <si>
+    <t>01388725508</t>
+  </si>
+  <si>
+    <t>01388725509</t>
+  </si>
+  <si>
+    <t>01388725510</t>
+  </si>
+  <si>
+    <t>01388725511</t>
+  </si>
+  <si>
+    <t>01388725512</t>
+  </si>
+  <si>
+    <t>01388725513</t>
+  </si>
+  <si>
+    <t>01388725514</t>
+  </si>
+  <si>
+    <t>01388725515</t>
+  </si>
+  <si>
+    <t>01388725516</t>
+  </si>
+  <si>
+    <t>01388725517</t>
+  </si>
+  <si>
+    <t>01388725518</t>
+  </si>
+  <si>
+    <t>01388725519</t>
+  </si>
+  <si>
+    <t>01388725520</t>
+  </si>
+  <si>
+    <t>01388725521</t>
+  </si>
+  <si>
+    <t>01388725522</t>
+  </si>
+  <si>
+    <t>01388725523</t>
+  </si>
+  <si>
+    <t>01388725524</t>
+  </si>
+  <si>
+    <t>01388725525</t>
+  </si>
+  <si>
+    <t>01388725526</t>
+  </si>
+  <si>
+    <t>01388725527</t>
+  </si>
+  <si>
+    <t>01388725528</t>
+  </si>
+  <si>
+    <t>01388725529</t>
+  </si>
+  <si>
+    <t>01388725530</t>
+  </si>
+  <si>
+    <t>01388725531</t>
+  </si>
+  <si>
+    <t>01388725532</t>
+  </si>
+  <si>
+    <t>01388725533</t>
   </si>
 </sst>
 </file>
@@ -2850,7 +3753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2858,12 +3761,19 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3144,26 +4054,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C301"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" style="6" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="4" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>53</v>
       </c>
@@ -3173,8 +4088,11 @@
       <c r="C2" s="2" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>54</v>
       </c>
@@ -3184,8 +4102,11 @@
       <c r="C3" s="2" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="5" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>55</v>
       </c>
@@ -3195,8 +4116,11 @@
       <c r="C4" s="2" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="5" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
@@ -3206,8 +4130,11 @@
       <c r="C5" s="2" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="5" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>57</v>
       </c>
@@ -3217,8 +4144,11 @@
       <c r="C6" s="2" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="5" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>58</v>
       </c>
@@ -3228,8 +4158,11 @@
       <c r="C7" s="2" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="5" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>59</v>
       </c>
@@ -3239,8 +4172,11 @@
       <c r="C8" s="2" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="5" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
@@ -3250,8 +4186,11 @@
       <c r="C9" s="2" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="5" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
@@ -3261,8 +4200,11 @@
       <c r="C10" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="5" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
@@ -3272,8 +4214,11 @@
       <c r="C11" s="2" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="5" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>63</v>
       </c>
@@ -3283,8 +4228,11 @@
       <c r="C12" s="2" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="5" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>64</v>
       </c>
@@ -3294,8 +4242,11 @@
       <c r="C13" s="2" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="5" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>65</v>
       </c>
@@ -3305,8 +4256,11 @@
       <c r="C14" s="2" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" s="5" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>66</v>
       </c>
@@ -3316,8 +4270,11 @@
       <c r="C15" s="2" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" s="5" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>67</v>
       </c>
@@ -3327,8 +4284,11 @@
       <c r="C16" s="2" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="5" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>68</v>
       </c>
@@ -3338,8 +4298,11 @@
       <c r="C17" s="2" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="5" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>69</v>
       </c>
@@ -3349,8 +4312,11 @@
       <c r="C18" s="2" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="5" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
@@ -3360,8 +4326,11 @@
       <c r="C19" s="2" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="5" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>71</v>
       </c>
@@ -3371,8 +4340,11 @@
       <c r="C20" s="2" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="5" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>72</v>
       </c>
@@ -3382,8 +4354,11 @@
       <c r="C21" s="2" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="5" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>73</v>
       </c>
@@ -3393,8 +4368,11 @@
       <c r="C22" s="2" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" s="5" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>74</v>
       </c>
@@ -3404,8 +4382,11 @@
       <c r="C23" s="2" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" s="5" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>75</v>
       </c>
@@ -3415,8 +4396,11 @@
       <c r="C24" s="2" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" s="5" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>76</v>
       </c>
@@ -3426,8 +4410,11 @@
       <c r="C25" s="2" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" s="5" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>77</v>
       </c>
@@ -3437,8 +4424,11 @@
       <c r="C26" s="2" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" s="5" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>78</v>
       </c>
@@ -3448,8 +4438,11 @@
       <c r="C27" s="2" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" s="5" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>79</v>
       </c>
@@ -3459,8 +4452,11 @@
       <c r="C28" s="2" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" s="5" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>80</v>
       </c>
@@ -3470,8 +4466,11 @@
       <c r="C29" s="2" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" s="5" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>81</v>
       </c>
@@ -3481,8 +4480,11 @@
       <c r="C30" s="2" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" s="5" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>82</v>
       </c>
@@ -3492,8 +4494,11 @@
       <c r="C31" s="2" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" s="5" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>83</v>
       </c>
@@ -3503,8 +4508,11 @@
       <c r="C32" s="2" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" s="5" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>84</v>
       </c>
@@ -3514,8 +4522,11 @@
       <c r="C33" s="2" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" s="5" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
@@ -3525,8 +4536,11 @@
       <c r="C34" s="2" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" s="5" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>86</v>
       </c>
@@ -3536,8 +4550,11 @@
       <c r="C35" s="2" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" s="5" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +4564,11 @@
       <c r="C36" s="2" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" s="5" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>88</v>
       </c>
@@ -3558,8 +4578,11 @@
       <c r="C37" s="2" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" s="5" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>89</v>
       </c>
@@ -3569,8 +4592,11 @@
       <c r="C38" s="2" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" s="5" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>90</v>
       </c>
@@ -3580,8 +4606,11 @@
       <c r="C39" s="2" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" s="5" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>91</v>
       </c>
@@ -3591,8 +4620,11 @@
       <c r="C40" s="2" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" s="5" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>92</v>
       </c>
@@ -3602,8 +4634,11 @@
       <c r="C41" s="2" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" s="5" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>93</v>
       </c>
@@ -3613,8 +4648,11 @@
       <c r="C42" s="2" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" s="5" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>94</v>
       </c>
@@ -3624,8 +4662,11 @@
       <c r="C43" s="2" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" s="5" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>95</v>
       </c>
@@ -3635,8 +4676,11 @@
       <c r="C44" s="2" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" s="5" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>96</v>
       </c>
@@ -3646,8 +4690,11 @@
       <c r="C45" s="2" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" s="5" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>97</v>
       </c>
@@ -3657,8 +4704,11 @@
       <c r="C46" s="2" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" s="5" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>98</v>
       </c>
@@ -3668,8 +4718,11 @@
       <c r="C47" s="2" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" s="5" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>99</v>
       </c>
@@ -3679,8 +4732,11 @@
       <c r="C48" s="2" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" s="5" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>100</v>
       </c>
@@ -3690,8 +4746,11 @@
       <c r="C49" s="2" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" s="5" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>101</v>
       </c>
@@ -3701,8 +4760,11 @@
       <c r="C50" s="2" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" s="5" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>102</v>
       </c>
@@ -3712,8 +4774,11 @@
       <c r="C51" s="2" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" s="5" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>103</v>
       </c>
@@ -3723,8 +4788,11 @@
       <c r="C52" s="2" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" s="5" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>104</v>
       </c>
@@ -3734,8 +4802,11 @@
       <c r="C53" s="2" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" s="5" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>105</v>
       </c>
@@ -3745,8 +4816,11 @@
       <c r="C54" s="2" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" s="5" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>106</v>
       </c>
@@ -3756,8 +4830,11 @@
       <c r="C55" s="2" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" s="5" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>107</v>
       </c>
@@ -3767,8 +4844,11 @@
       <c r="C56" s="2" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" s="5" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>108</v>
       </c>
@@ -3778,8 +4858,11 @@
       <c r="C57" s="2" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" s="5" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>109</v>
       </c>
@@ -3789,8 +4872,11 @@
       <c r="C58" s="2" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" s="5" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>110</v>
       </c>
@@ -3800,8 +4886,11 @@
       <c r="C59" s="2" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" s="5" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>111</v>
       </c>
@@ -3811,8 +4900,11 @@
       <c r="C60" s="2" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" s="5" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>112</v>
       </c>
@@ -3822,8 +4914,11 @@
       <c r="C61" s="2" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" s="5" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>113</v>
       </c>
@@ -3833,8 +4928,11 @@
       <c r="C62" s="2" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" s="5" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>114</v>
       </c>
@@ -3844,8 +4942,11 @@
       <c r="C63" s="2" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" s="5" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>115</v>
       </c>
@@ -3855,8 +4956,11 @@
       <c r="C64" s="2" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" s="5" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>116</v>
       </c>
@@ -3866,8 +4970,11 @@
       <c r="C65" s="2" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" s="5" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>117</v>
       </c>
@@ -3877,8 +4984,11 @@
       <c r="C66" s="2" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" s="5" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>118</v>
       </c>
@@ -3888,8 +4998,11 @@
       <c r="C67" s="2" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" s="5" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>119</v>
       </c>
@@ -3899,8 +5012,11 @@
       <c r="C68" s="2" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" s="5" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>120</v>
       </c>
@@ -3910,8 +5026,11 @@
       <c r="C69" s="2" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" s="5" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>121</v>
       </c>
@@ -3921,8 +5040,11 @@
       <c r="C70" s="2" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" s="5" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>122</v>
       </c>
@@ -3932,8 +5054,11 @@
       <c r="C71" s="2" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" s="5" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>123</v>
       </c>
@@ -3943,8 +5068,11 @@
       <c r="C72" s="2" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" s="5" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>124</v>
       </c>
@@ -3954,8 +5082,11 @@
       <c r="C73" s="2" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" s="5" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>125</v>
       </c>
@@ -3965,8 +5096,11 @@
       <c r="C74" s="2" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" s="5" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>126</v>
       </c>
@@ -3976,8 +5110,11 @@
       <c r="C75" s="2" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>127</v>
       </c>
@@ -3987,8 +5124,11 @@
       <c r="C76" s="2" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" s="5" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>128</v>
       </c>
@@ -3998,8 +5138,11 @@
       <c r="C77" s="2" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" s="5" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>129</v>
       </c>
@@ -4009,8 +5152,11 @@
       <c r="C78" s="2" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" s="5" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>130</v>
       </c>
@@ -4020,8 +5166,11 @@
       <c r="C79" s="2" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" s="5" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>131</v>
       </c>
@@ -4031,8 +5180,11 @@
       <c r="C80" s="2" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" s="5" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>132</v>
       </c>
@@ -4042,8 +5194,11 @@
       <c r="C81" s="2" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" s="5" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>133</v>
       </c>
@@ -4053,8 +5208,11 @@
       <c r="C82" s="2" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" s="5" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>134</v>
       </c>
@@ -4064,8 +5222,11 @@
       <c r="C83" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" s="5" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>135</v>
       </c>
@@ -4075,8 +5236,11 @@
       <c r="C84" s="2" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" s="5" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>136</v>
       </c>
@@ -4086,8 +5250,11 @@
       <c r="C85" s="2" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" s="5" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>137</v>
       </c>
@@ -4097,8 +5264,11 @@
       <c r="C86" s="2" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" s="5" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>138</v>
       </c>
@@ -4108,8 +5278,11 @@
       <c r="C87" s="2" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" s="5" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>139</v>
       </c>
@@ -4119,8 +5292,11 @@
       <c r="C88" s="2" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" s="5" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>140</v>
       </c>
@@ -4130,8 +5306,11 @@
       <c r="C89" s="2" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" s="5" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>141</v>
       </c>
@@ -4141,8 +5320,11 @@
       <c r="C90" s="2" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" s="5" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>142</v>
       </c>
@@ -4152,8 +5334,11 @@
       <c r="C91" s="2" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" s="5" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>143</v>
       </c>
@@ -4163,8 +5348,11 @@
       <c r="C92" s="2" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" s="5" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>144</v>
       </c>
@@ -4174,8 +5362,11 @@
       <c r="C93" s="2" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" s="5" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>145</v>
       </c>
@@ -4185,8 +5376,11 @@
       <c r="C94" s="2" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" s="5" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>146</v>
       </c>
@@ -4196,8 +5390,11 @@
       <c r="C95" s="2" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" s="5" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>147</v>
       </c>
@@ -4207,8 +5404,11 @@
       <c r="C96" s="2" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" s="5" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>148</v>
       </c>
@@ -4218,8 +5418,11 @@
       <c r="C97" s="2" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" s="5" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>149</v>
       </c>
@@ -4229,8 +5432,11 @@
       <c r="C98" s="2" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" s="5" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>150</v>
       </c>
@@ -4240,8 +5446,11 @@
       <c r="C99" s="2" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" s="5" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>151</v>
       </c>
@@ -4251,8 +5460,11 @@
       <c r="C100" s="2" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" s="5" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>152</v>
       </c>
@@ -4262,8 +5474,11 @@
       <c r="C101" s="2" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" s="5" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>153</v>
       </c>
@@ -4273,8 +5488,11 @@
       <c r="C102" s="2" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" s="5" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>154</v>
       </c>
@@ -4284,8 +5502,11 @@
       <c r="C103" s="2" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" s="5" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>155</v>
       </c>
@@ -4295,8 +5516,11 @@
       <c r="C104" s="2" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" s="5" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>156</v>
       </c>
@@ -4306,8 +5530,11 @@
       <c r="C105" s="2" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" s="5" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>157</v>
       </c>
@@ -4317,8 +5544,11 @@
       <c r="C106" s="2" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" s="5" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>158</v>
       </c>
@@ -4328,8 +5558,11 @@
       <c r="C107" s="2" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" s="5" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>159</v>
       </c>
@@ -4339,8 +5572,11 @@
       <c r="C108" s="2" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" s="5" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>160</v>
       </c>
@@ -4350,8 +5586,11 @@
       <c r="C109" s="2" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" s="5" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>161</v>
       </c>
@@ -4361,8 +5600,11 @@
       <c r="C110" s="2" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" s="5" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>162</v>
       </c>
@@ -4372,8 +5614,11 @@
       <c r="C111" s="2" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" s="5" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>163</v>
       </c>
@@ -4383,8 +5628,11 @@
       <c r="C112" s="2" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" s="5" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>164</v>
       </c>
@@ -4394,8 +5642,11 @@
       <c r="C113" s="2" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" s="5" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>165</v>
       </c>
@@ -4405,8 +5656,11 @@
       <c r="C114" s="2" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" s="5" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>166</v>
       </c>
@@ -4416,8 +5670,11 @@
       <c r="C115" s="2" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" s="5" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>167</v>
       </c>
@@ -4427,8 +5684,11 @@
       <c r="C116" s="2" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" s="5" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>168</v>
       </c>
@@ -4438,8 +5698,11 @@
       <c r="C117" s="2" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" s="5" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>169</v>
       </c>
@@ -4449,8 +5712,11 @@
       <c r="C118" s="2" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" s="5" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>170</v>
       </c>
@@ -4460,8 +5726,11 @@
       <c r="C119" s="2" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" s="5" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>171</v>
       </c>
@@ -4471,8 +5740,11 @@
       <c r="C120" s="2" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" s="5" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>172</v>
       </c>
@@ -4482,8 +5754,11 @@
       <c r="C121" s="2" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" s="5" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>173</v>
       </c>
@@ -4493,8 +5768,11 @@
       <c r="C122" s="2" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" s="5" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>174</v>
       </c>
@@ -4504,8 +5782,11 @@
       <c r="C123" s="2" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" s="5" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>175</v>
       </c>
@@ -4515,8 +5796,11 @@
       <c r="C124" s="2" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" s="5" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>176</v>
       </c>
@@ -4526,8 +5810,11 @@
       <c r="C125" s="2" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" s="5" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>177</v>
       </c>
@@ -4537,8 +5824,11 @@
       <c r="C126" s="2" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" s="5" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>178</v>
       </c>
@@ -4548,8 +5838,11 @@
       <c r="C127" s="2" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" s="5" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>179</v>
       </c>
@@ -4559,8 +5852,11 @@
       <c r="C128" s="2" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" s="5" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>180</v>
       </c>
@@ -4570,8 +5866,11 @@
       <c r="C129" s="2" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" s="5" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>181</v>
       </c>
@@ -4581,8 +5880,11 @@
       <c r="C130" s="2" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" s="5" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>182</v>
       </c>
@@ -4592,8 +5894,11 @@
       <c r="C131" s="2" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" s="5" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>183</v>
       </c>
@@ -4603,8 +5908,11 @@
       <c r="C132" s="2" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" s="5" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>184</v>
       </c>
@@ -4614,8 +5922,11 @@
       <c r="C133" s="2" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" s="5" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>185</v>
       </c>
@@ -4625,8 +5936,11 @@
       <c r="C134" s="2" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" s="5" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>186</v>
       </c>
@@ -4636,8 +5950,11 @@
       <c r="C135" s="2" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" s="5" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>187</v>
       </c>
@@ -4647,8 +5964,11 @@
       <c r="C136" s="2" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" s="5" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>188</v>
       </c>
@@ -4658,8 +5978,11 @@
       <c r="C137" s="2" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" s="5" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>189</v>
       </c>
@@ -4669,8 +5992,11 @@
       <c r="C138" s="2" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" s="5" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>190</v>
       </c>
@@ -4680,8 +6006,11 @@
       <c r="C139" s="2" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" s="5" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>191</v>
       </c>
@@ -4691,8 +6020,11 @@
       <c r="C140" s="2" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" s="5" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>192</v>
       </c>
@@ -4702,8 +6034,11 @@
       <c r="C141" s="2" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" s="5" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>193</v>
       </c>
@@ -4713,8 +6048,11 @@
       <c r="C142" s="2" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" s="5" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>194</v>
       </c>
@@ -4724,8 +6062,11 @@
       <c r="C143" s="2" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" s="5" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>195</v>
       </c>
@@ -4735,8 +6076,11 @@
       <c r="C144" s="2" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" s="5" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>196</v>
       </c>
@@ -4746,8 +6090,11 @@
       <c r="C145" s="2" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" s="5" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>197</v>
       </c>
@@ -4757,8 +6104,11 @@
       <c r="C146" s="2" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" s="5" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>198</v>
       </c>
@@ -4768,8 +6118,11 @@
       <c r="C147" s="2" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" s="5" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>199</v>
       </c>
@@ -4779,8 +6132,11 @@
       <c r="C148" s="2" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" s="5" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>200</v>
       </c>
@@ -4790,8 +6146,11 @@
       <c r="C149" s="2" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" s="5" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>201</v>
       </c>
@@ -4801,8 +6160,11 @@
       <c r="C150" s="2" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" s="5" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>202</v>
       </c>
@@ -4812,8 +6174,11 @@
       <c r="C151" s="2" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" s="5" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>203</v>
       </c>
@@ -4823,8 +6188,11 @@
       <c r="C152" s="2" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" s="5" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>204</v>
       </c>
@@ -4834,8 +6202,11 @@
       <c r="C153" s="2" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" s="5" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>205</v>
       </c>
@@ -4845,8 +6216,11 @@
       <c r="C154" s="2" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" s="5" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>206</v>
       </c>
@@ -4856,8 +6230,11 @@
       <c r="C155" s="2" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" s="5" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>207</v>
       </c>
@@ -4867,8 +6244,11 @@
       <c r="C156" s="2" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" s="5" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>208</v>
       </c>
@@ -4878,8 +6258,11 @@
       <c r="C157" s="2" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" s="5" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>209</v>
       </c>
@@ -4889,8 +6272,11 @@
       <c r="C158" s="2" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" s="5" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>210</v>
       </c>
@@ -4900,8 +6286,11 @@
       <c r="C159" s="2" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" s="5" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>211</v>
       </c>
@@ -4911,8 +6300,11 @@
       <c r="C160" s="2" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" s="5" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>212</v>
       </c>
@@ -4922,8 +6314,11 @@
       <c r="C161" s="2" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" s="5" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>213</v>
       </c>
@@ -4933,8 +6328,11 @@
       <c r="C162" s="2" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" s="5" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>214</v>
       </c>
@@ -4944,8 +6342,11 @@
       <c r="C163" s="2" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" s="5" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>215</v>
       </c>
@@ -4955,8 +6356,11 @@
       <c r="C164" s="2" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" s="5" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>216</v>
       </c>
@@ -4966,8 +6370,11 @@
       <c r="C165" s="2" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" s="5" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>217</v>
       </c>
@@ -4977,8 +6384,11 @@
       <c r="C166" s="2" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" s="5" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>218</v>
       </c>
@@ -4988,8 +6398,11 @@
       <c r="C167" s="2" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" s="5" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>219</v>
       </c>
@@ -4999,8 +6412,11 @@
       <c r="C168" s="2" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" s="5" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>220</v>
       </c>
@@ -5010,8 +6426,11 @@
       <c r="C169" s="2" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169" s="5" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>221</v>
       </c>
@@ -5021,8 +6440,11 @@
       <c r="C170" s="2" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" s="5" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>222</v>
       </c>
@@ -5032,8 +6454,11 @@
       <c r="C171" s="2" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" s="5" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>223</v>
       </c>
@@ -5043,8 +6468,11 @@
       <c r="C172" s="2" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172" s="5" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>224</v>
       </c>
@@ -5054,8 +6482,11 @@
       <c r="C173" s="2" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" s="5" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>225</v>
       </c>
@@ -5065,8 +6496,11 @@
       <c r="C174" s="2" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" s="5" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>226</v>
       </c>
@@ -5076,8 +6510,11 @@
       <c r="C175" s="2" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175" s="5" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>227</v>
       </c>
@@ -5087,8 +6524,11 @@
       <c r="C176" s="2" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176" s="5" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>228</v>
       </c>
@@ -5098,8 +6538,11 @@
       <c r="C177" s="2" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177" s="5" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>229</v>
       </c>
@@ -5109,8 +6552,11 @@
       <c r="C178" s="2" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178" s="5" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>230</v>
       </c>
@@ -5120,8 +6566,11 @@
       <c r="C179" s="2" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179" s="5" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>231</v>
       </c>
@@ -5131,8 +6580,11 @@
       <c r="C180" s="2" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180" s="5" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>232</v>
       </c>
@@ -5142,8 +6594,11 @@
       <c r="C181" s="2" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181" s="5" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>233</v>
       </c>
@@ -5153,8 +6608,11 @@
       <c r="C182" s="2" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182" s="5" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>234</v>
       </c>
@@ -5164,8 +6622,11 @@
       <c r="C183" s="2" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183" s="5" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>235</v>
       </c>
@@ -5175,8 +6636,11 @@
       <c r="C184" s="2" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184" s="5" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>236</v>
       </c>
@@ -5186,8 +6650,11 @@
       <c r="C185" s="2" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185" s="5" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>237</v>
       </c>
@@ -5197,8 +6664,11 @@
       <c r="C186" s="2" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186" s="5" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>238</v>
       </c>
@@ -5208,8 +6678,11 @@
       <c r="C187" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187" s="5" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>239</v>
       </c>
@@ -5219,8 +6692,11 @@
       <c r="C188" s="2" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188" s="5" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>240</v>
       </c>
@@ -5230,8 +6706,11 @@
       <c r="C189" s="2" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189" s="5" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>241</v>
       </c>
@@ -5241,8 +6720,11 @@
       <c r="C190" s="2" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190" s="5" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>242</v>
       </c>
@@ -5252,8 +6734,11 @@
       <c r="C191" s="2" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191" s="5" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>243</v>
       </c>
@@ -5263,8 +6748,11 @@
       <c r="C192" s="2" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192" s="5" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>244</v>
       </c>
@@ -5274,8 +6762,11 @@
       <c r="C193" s="2" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193" s="5" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>245</v>
       </c>
@@ -5285,8 +6776,11 @@
       <c r="C194" s="2" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194" s="5" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>246</v>
       </c>
@@ -5296,8 +6790,11 @@
       <c r="C195" s="2" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195" s="5" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>247</v>
       </c>
@@ -5307,8 +6804,11 @@
       <c r="C196" s="2" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196" s="5" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>248</v>
       </c>
@@ -5318,8 +6818,11 @@
       <c r="C197" s="2" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197" s="5" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>249</v>
       </c>
@@ -5329,8 +6832,11 @@
       <c r="C198" s="2" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198" s="5" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>250</v>
       </c>
@@ -5340,8 +6846,11 @@
       <c r="C199" s="2" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199" s="5" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>251</v>
       </c>
@@ -5351,8 +6860,11 @@
       <c r="C200" s="2" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200" s="5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>252</v>
       </c>
@@ -5362,8 +6874,11 @@
       <c r="C201" s="2" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201" s="5" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>253</v>
       </c>
@@ -5373,8 +6888,11 @@
       <c r="C202" s="2" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202" s="5" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>254</v>
       </c>
@@ -5384,8 +6902,11 @@
       <c r="C203" s="2" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D203" s="5" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>255</v>
       </c>
@@ -5395,8 +6916,11 @@
       <c r="C204" s="2" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D204" s="5" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>256</v>
       </c>
@@ -5406,8 +6930,11 @@
       <c r="C205" s="2" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D205" s="5" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>257</v>
       </c>
@@ -5417,8 +6944,11 @@
       <c r="C206" s="2" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D206" s="5" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>258</v>
       </c>
@@ -5428,8 +6958,11 @@
       <c r="C207" s="2" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D207" s="5" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>259</v>
       </c>
@@ -5439,8 +6972,11 @@
       <c r="C208" s="2" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D208" s="5" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>260</v>
       </c>
@@ -5450,8 +6986,11 @@
       <c r="C209" s="2" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D209" s="5" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>261</v>
       </c>
@@ -5461,8 +7000,11 @@
       <c r="C210" s="2" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D210" s="5" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>262</v>
       </c>
@@ -5472,8 +7014,11 @@
       <c r="C211" s="2" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D211" s="5" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>263</v>
       </c>
@@ -5483,8 +7028,11 @@
       <c r="C212" s="2" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D212" s="5" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>264</v>
       </c>
@@ -5494,8 +7042,11 @@
       <c r="C213" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D213" s="5" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>265</v>
       </c>
@@ -5505,8 +7056,11 @@
       <c r="C214" s="2" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D214" s="5" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>266</v>
       </c>
@@ -5516,8 +7070,11 @@
       <c r="C215" s="2" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D215" s="5" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>267</v>
       </c>
@@ -5527,8 +7084,11 @@
       <c r="C216" s="2" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D216" s="5" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>268</v>
       </c>
@@ -5538,8 +7098,11 @@
       <c r="C217" s="2" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D217" s="5" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>269</v>
       </c>
@@ -5549,8 +7112,11 @@
       <c r="C218" s="2" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D218" s="5" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>270</v>
       </c>
@@ -5560,8 +7126,11 @@
       <c r="C219" s="2" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D219" s="5" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>271</v>
       </c>
@@ -5571,8 +7140,11 @@
       <c r="C220" s="2" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D220" s="5" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>820</v>
       </c>
@@ -5582,8 +7154,11 @@
       <c r="C221" s="2" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D221" s="5" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>821</v>
       </c>
@@ -5593,8 +7168,11 @@
       <c r="C222" s="2" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D222" s="5" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>822</v>
       </c>
@@ -5604,8 +7182,11 @@
       <c r="C223" s="2" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D223" s="5" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>823</v>
       </c>
@@ -5615,8 +7196,11 @@
       <c r="C224" s="2" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D224" s="5" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>824</v>
       </c>
@@ -5626,8 +7210,11 @@
       <c r="C225" s="2" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D225" s="5" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>825</v>
       </c>
@@ -5637,8 +7224,11 @@
       <c r="C226" s="2" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D226" s="5" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>826</v>
       </c>
@@ -5648,8 +7238,11 @@
       <c r="C227" s="2" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D227" s="5" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>827</v>
       </c>
@@ -5659,8 +7252,11 @@
       <c r="C228" s="2" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D228" s="5" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>828</v>
       </c>
@@ -5670,8 +7266,11 @@
       <c r="C229" s="2" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D229" s="5" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>829</v>
       </c>
@@ -5681,8 +7280,11 @@
       <c r="C230" s="2" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D230" s="5" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>830</v>
       </c>
@@ -5692,8 +7294,11 @@
       <c r="C231" s="2" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D231" s="5" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>831</v>
       </c>
@@ -5703,8 +7308,11 @@
       <c r="C232" s="2" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D232" s="5" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>832</v>
       </c>
@@ -5714,8 +7322,11 @@
       <c r="C233" s="2" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D233" s="5" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>833</v>
       </c>
@@ -5725,8 +7336,11 @@
       <c r="C234" s="2" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D234" s="5" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>834</v>
       </c>
@@ -5736,8 +7350,11 @@
       <c r="C235" s="2" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D235" s="5" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>835</v>
       </c>
@@ -5747,8 +7364,11 @@
       <c r="C236" s="2" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D236" s="5" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>836</v>
       </c>
@@ -5758,8 +7378,11 @@
       <c r="C237" s="2" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D237" s="5" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>837</v>
       </c>
@@ -5769,8 +7392,11 @@
       <c r="C238" s="2" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D238" s="5" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>838</v>
       </c>
@@ -5780,8 +7406,11 @@
       <c r="C239" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D239" s="5" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>839</v>
       </c>
@@ -5791,8 +7420,11 @@
       <c r="C240" s="2" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D240" s="5" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>840</v>
       </c>
@@ -5802,8 +7434,11 @@
       <c r="C241" s="2" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D241" s="5" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>841</v>
       </c>
@@ -5813,8 +7448,11 @@
       <c r="C242" s="2" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D242" s="5" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>842</v>
       </c>
@@ -5824,8 +7462,11 @@
       <c r="C243" s="2" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D243" s="5" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>843</v>
       </c>
@@ -5835,8 +7476,11 @@
       <c r="C244" s="2" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D244" s="5" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>844</v>
       </c>
@@ -5846,8 +7490,11 @@
       <c r="C245" s="2" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D245" s="5" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>845</v>
       </c>
@@ -5857,8 +7504,11 @@
       <c r="C246" s="2" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D246" s="5" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>846</v>
       </c>
@@ -5868,8 +7518,11 @@
       <c r="C247" s="2" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D247" s="5" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>847</v>
       </c>
@@ -5879,8 +7532,11 @@
       <c r="C248" s="2" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D248" s="5" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>848</v>
       </c>
@@ -5890,8 +7546,11 @@
       <c r="C249" s="2" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D249" s="5" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>849</v>
       </c>
@@ -5901,8 +7560,11 @@
       <c r="C250" s="2" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D250" s="5" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>850</v>
       </c>
@@ -5912,547 +7574,697 @@
       <c r="C251" s="2" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D251" s="5" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="B252" s="3" t="s">
+      <c r="B252" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="C252" s="3" t="s">
+      <c r="C252" s="2" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D252" s="5" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="B253" s="3" t="s">
+      <c r="B253" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="C253" s="3" t="s">
+      <c r="C253" s="2" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D253" s="5" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>853</v>
       </c>
-      <c r="B254" s="3" t="s">
+      <c r="B254" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="C254" s="3" t="s">
+      <c r="C254" s="2" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D254" s="5" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="B255" s="3" t="s">
+      <c r="B255" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="C255" s="3" t="s">
+      <c r="C255" s="2" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D255" s="5" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="B256" s="3" t="s">
+      <c r="B256" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="C256" s="3" t="s">
+      <c r="C256" s="2" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D256" s="5" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B257" s="3" t="s">
+      <c r="B257" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="C257" s="3" t="s">
+      <c r="C257" s="2" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D257" s="5" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="B258" s="3" t="s">
+      <c r="B258" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="C258" s="3" t="s">
+      <c r="C258" s="2" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D258" s="5" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="B259" s="3" t="s">
+      <c r="B259" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="C259" s="3" t="s">
+      <c r="C259" s="2" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D259" s="5" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="B260" s="3" t="s">
+      <c r="B260" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="C260" s="3" t="s">
+      <c r="C260" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D260" s="5" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="B261" s="3" t="s">
+      <c r="B261" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="C261" s="3" t="s">
+      <c r="C261" s="2" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D261" s="5" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="B262" s="3" t="s">
+      <c r="B262" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="C262" s="3" t="s">
+      <c r="C262" s="2" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D262" s="5" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="B263" s="3" t="s">
+      <c r="B263" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="C263" s="3" t="s">
+      <c r="C263" s="2" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D263" s="5" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="B264" s="3" t="s">
+      <c r="B264" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="C264" s="3" t="s">
+      <c r="C264" s="2" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D264" s="5" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="B265" s="3" t="s">
+      <c r="B265" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="C265" s="3" t="s">
+      <c r="C265" s="2" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D265" s="5" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="B266" s="3" t="s">
+      <c r="B266" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="C266" s="3" t="s">
+      <c r="C266" s="2" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D266" s="5" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="B267" s="3" t="s">
+      <c r="B267" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="C267" s="3" t="s">
+      <c r="C267" s="2" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D267" s="5" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="B268" s="3" t="s">
+      <c r="B268" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="C268" s="3" t="s">
+      <c r="C268" s="2" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D268" s="5" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="B269" s="3" t="s">
+      <c r="B269" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="C269" s="3" t="s">
+      <c r="C269" s="2" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D269" s="5" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="B270" s="3" t="s">
+      <c r="B270" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="C270" s="3" t="s">
+      <c r="C270" s="2" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D270" s="5" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="B271" s="3" t="s">
+      <c r="B271" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="C271" s="3" t="s">
+      <c r="C271" s="2" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D271" s="5" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="B272" s="3" t="s">
+      <c r="B272" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="C272" s="3" t="s">
+      <c r="C272" s="2" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D272" s="5" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="B273" s="3" t="s">
+      <c r="B273" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="C273" s="3" t="s">
+      <c r="C273" s="2" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D273" s="5" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="B274" s="3" t="s">
+      <c r="B274" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="C274" s="3" t="s">
+      <c r="C274" s="2" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D274" s="5" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="B275" s="3" t="s">
+      <c r="B275" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="C275" s="3" t="s">
+      <c r="C275" s="2" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D275" s="5" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="B276" s="3" t="s">
+      <c r="B276" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="C276" s="3" t="s">
+      <c r="C276" s="2" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D276" s="5" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="B277" s="3" t="s">
+      <c r="B277" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="C277" s="3" t="s">
+      <c r="C277" s="2" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D277" s="5" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="B278" s="3" t="s">
+      <c r="B278" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="C278" s="3" t="s">
+      <c r="C278" s="2" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D278" s="5" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="B279" s="3" t="s">
+      <c r="B279" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="C279" s="3" t="s">
+      <c r="C279" s="2" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D279" s="5" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="B280" s="3" t="s">
+      <c r="B280" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="C280" s="3" t="s">
+      <c r="C280" s="2" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D280" s="5" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="B281" s="3" t="s">
+      <c r="B281" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="C281" s="3" t="s">
+      <c r="C281" s="2" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D281" s="5" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="B282" s="3" t="s">
+      <c r="B282" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="C282" s="3" t="s">
+      <c r="C282" s="2" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D282" s="5" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="B283" s="3" t="s">
+      <c r="B283" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="C283" s="3" t="s">
+      <c r="C283" s="2" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D283" s="5" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="B284" s="3" t="s">
+      <c r="B284" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="C284" s="3" t="s">
+      <c r="C284" s="2" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D284" s="5" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="B285" s="3" t="s">
+      <c r="B285" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="C285" s="3" t="s">
+      <c r="C285" s="2" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D285" s="5" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="B286" s="3" t="s">
+      <c r="B286" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="C286" s="3" t="s">
+      <c r="C286" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D286" s="5" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="B287" s="3" t="s">
+      <c r="B287" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="C287" s="3" t="s">
+      <c r="C287" s="2" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D287" s="5" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="B288" s="3" t="s">
+      <c r="B288" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="C288" s="3" t="s">
+      <c r="C288" s="2" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D288" s="5" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="B289" s="3" t="s">
+      <c r="B289" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="C289" s="3" t="s">
+      <c r="C289" s="2" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D289" s="5" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="B290" s="3" t="s">
+      <c r="B290" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="C290" s="3" t="s">
+      <c r="C290" s="2" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D290" s="5" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="B291" s="3" t="s">
+      <c r="B291" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="C291" s="3" t="s">
+      <c r="C291" s="2" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D291" s="5" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="B292" s="3" t="s">
+      <c r="B292" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="C292" s="3" t="s">
+      <c r="C292" s="2" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D292" s="5" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="B293" s="3" t="s">
+      <c r="B293" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="C293" s="3" t="s">
+      <c r="C293" s="2" t="s">
         <v>812</v>
       </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D293" s="5" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="B294" s="3" t="s">
+      <c r="B294" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="C294" s="3" t="s">
+      <c r="C294" s="2" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D294" s="5" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="B295" s="3" t="s">
+      <c r="B295" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C295" s="3" t="s">
+      <c r="C295" s="2" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D295" s="5" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B296" s="3" t="s">
+      <c r="B296" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="C296" s="3" t="s">
+      <c r="C296" s="2" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D296" s="5" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="B297" s="3" t="s">
+      <c r="B297" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="C297" s="3" t="s">
+      <c r="C297" s="2" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D297" s="5" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="B298" s="3" t="s">
+      <c r="B298" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="C298" s="3" t="s">
+      <c r="C298" s="2" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D298" s="5" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="B299" s="3" t="s">
+      <c r="B299" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="C299" s="3" t="s">
+      <c r="C299" s="2" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D299" s="5" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="B300" s="3" t="s">
+      <c r="B300" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="C300" s="3" t="s">
+      <c r="C300" s="2" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D300" s="5" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>900</v>
       </c>
@@ -6461,6 +8273,9 @@
       </c>
       <c r="C301" s="2" t="s">
         <v>902</v>
+      </c>
+      <c r="D301" s="5" t="s">
+        <v>1203</v>
       </c>
     </row>
   </sheetData>
